--- a/output/quickfixclose_all_markets_daily.xlsx
+++ b/output/quickfixclose_all_markets_daily.xlsx
@@ -2538,7 +2538,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixclose daily (exit = the entry bar's own close, flat the same day), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-27); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-28 22:50 UTC.</t>
+          <t>quickfixclose daily (exit = the entry bar's own close, flat the same day), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-27); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-29 02:46 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/quickfixclose_all_markets_daily.xlsx
+++ b/output/quickfixclose_all_markets_daily.xlsx
@@ -549,11 +549,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F2" t="n">
         <v>7</v>
@@ -597,11 +597,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F3" t="n">
         <v>6</v>
@@ -645,11 +645,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F4" t="n">
         <v>10</v>
@@ -693,17 +693,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -721,10 +721,10 @@
         <v>100</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>10.33</v>
+        <v>12.33</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>110329.93</v>
+        <v>112329.66</v>
       </c>
     </row>
     <row r="6">
@@ -741,11 +741,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
@@ -789,11 +789,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F7" t="n">
         <v>3</v>
@@ -837,11 +837,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -885,11 +885,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F9" t="n">
         <v>3</v>
@@ -933,11 +933,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
@@ -981,11 +981,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F11" t="n">
         <v>4</v>
@@ -1029,11 +1029,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F12" t="n">
         <v>4</v>
@@ -1066,7 +1066,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -1077,17 +1077,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1105,31 +1105,31 @@
         <v>100</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2.23</v>
+        <v>3.34</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>102229.41</v>
+        <v>103337.33</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
@@ -1153,37 +1153,37 @@
         <v>100</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>102127.47</v>
+        <v>102229.41</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1201,10 +1201,10 @@
         <v>100</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>102031.33</v>
+        <v>102127.47</v>
       </c>
     </row>
     <row r="16">
@@ -1221,11 +1221,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F16" t="n">
         <v>3</v>
@@ -1269,11 +1269,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F17" t="n">
         <v>2</v>
@@ -1317,11 +1317,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F18" t="n">
         <v>2</v>
@@ -1365,11 +1365,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F19" t="n">
         <v>2</v>
@@ -1413,11 +1413,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
@@ -1461,11 +1461,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1506,11 +1506,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1551,11 +1551,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1596,11 +1596,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1641,11 +1641,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1686,11 +1686,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -2538,7 +2538,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixclose daily (exit = the entry bar's own close, flat the same day), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-27); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-29 02:46 UTC.</t>
+          <t>quickfixclose daily (exit = the entry bar's own close, flat the same day), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-29); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-30 20:33 UTC.</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O104"/>
+  <dimension ref="A1:O106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -6109,11 +6109,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -6122,25 +6122,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F66" t="n">
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>1360.4</v>
+        <v>2.69</v>
       </c>
       <c r="H66" t="n">
-        <v>1343.4</v>
+        <v>2.665</v>
       </c>
       <c r="J66" t="n">
-        <v>1385.9</v>
+        <v>2.722</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -6148,16 +6148,16 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="N66" t="n">
-        <v>100000</v>
+        <v>102031.33</v>
       </c>
       <c r="O66" t="n">
-        <v>101500</v>
+        <v>103337.33</v>
       </c>
     </row>
     <row r="67">
@@ -6167,7 +6167,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -6176,25 +6176,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="F67" t="n">
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>1167</v>
+        <v>1360.4</v>
       </c>
       <c r="H67" t="n">
-        <v>1159.4</v>
+        <v>1343.4</v>
       </c>
       <c r="J67" t="n">
-        <v>1193.2</v>
+        <v>1385.9</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -6202,53 +6202,53 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>3.4474</v>
+        <v>1.5</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>3.4474</v>
+        <v>1.5</v>
       </c>
       <c r="N67" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O67" t="n">
         <v>101500</v>
-      </c>
-      <c r="O67" t="n">
-        <v>104999.08</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F68" t="n">
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>2084.6</v>
+        <v>1167</v>
       </c>
       <c r="H68" t="n">
-        <v>2113.7</v>
+        <v>1159.4</v>
       </c>
       <c r="J68" t="n">
-        <v>2062.3</v>
+        <v>1193.2</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -6256,16 +6256,16 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0.7663</v>
+        <v>3.4474</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>0.7663</v>
+        <v>3.4474</v>
       </c>
       <c r="N68" t="n">
-        <v>100000</v>
+        <v>101500</v>
       </c>
       <c r="O68" t="n">
-        <v>100766.32</v>
+        <v>104999.08</v>
       </c>
     </row>
     <row r="69">
@@ -6275,34 +6275,34 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F69" t="n">
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>1641.5</v>
+        <v>2084.6</v>
       </c>
       <c r="H69" t="n">
-        <v>1621</v>
+        <v>2113.7</v>
       </c>
       <c r="J69" t="n">
-        <v>1662</v>
+        <v>2062.3</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -6310,16 +6310,16 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1</v>
+        <v>0.7663</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1</v>
+        <v>0.7663</v>
       </c>
       <c r="N69" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O69" t="n">
         <v>100766.32</v>
-      </c>
-      <c r="O69" t="n">
-        <v>101773.99</v>
       </c>
     </row>
     <row r="70">
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -6338,25 +6338,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F70" t="n">
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>1581.5</v>
+        <v>1641.5</v>
       </c>
       <c r="H70" t="n">
-        <v>1547.6</v>
+        <v>1621</v>
       </c>
       <c r="J70" t="n">
-        <v>1603</v>
+        <v>1662</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -6364,16 +6364,16 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0.6342</v>
+        <v>1</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>0.6342</v>
+        <v>1</v>
       </c>
       <c r="N70" t="n">
+        <v>100766.32</v>
+      </c>
+      <c r="O70" t="n">
         <v>101773.99</v>
-      </c>
-      <c r="O70" t="n">
-        <v>102419.46</v>
       </c>
     </row>
     <row r="71">
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -6392,25 +6392,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F71" t="n">
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>1559</v>
+        <v>1581.5</v>
       </c>
       <c r="H71" t="n">
-        <v>1539.5</v>
+        <v>1547.6</v>
       </c>
       <c r="J71" t="n">
-        <v>1599.9</v>
+        <v>1603</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -6418,53 +6418,53 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.0974</v>
+        <v>0.6342</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>2.0974</v>
+        <v>0.6342</v>
       </c>
       <c r="N71" t="n">
+        <v>101773.99</v>
+      </c>
+      <c r="O71" t="n">
         <v>102419.46</v>
-      </c>
-      <c r="O71" t="n">
-        <v>104567.64</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F72" t="n">
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>27907</v>
+        <v>1559</v>
       </c>
       <c r="H72" t="n">
-        <v>27965.76</v>
+        <v>1539.5</v>
       </c>
       <c r="J72" t="n">
-        <v>27776</v>
+        <v>1599.9</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -6472,22 +6472,22 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.2294</v>
+        <v>2.0974</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2.2294</v>
+        <v>2.0974</v>
       </c>
       <c r="N72" t="n">
-        <v>100000</v>
+        <v>102419.46</v>
       </c>
       <c r="O72" t="n">
-        <v>102229.41</v>
+        <v>104567.64</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -6500,25 +6500,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F73" t="n">
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>7206.55</v>
+        <v>27907</v>
       </c>
       <c r="H73" t="n">
-        <v>7223.26</v>
+        <v>27965.76</v>
       </c>
       <c r="J73" t="n">
-        <v>7171</v>
+        <v>27776</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -6526,22 +6526,22 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.1275</v>
+        <v>2.2294</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>2.1275</v>
+        <v>2.2294</v>
       </c>
       <c r="N73" t="n">
         <v>100000</v>
       </c>
       <c r="O73" t="n">
-        <v>102127.47</v>
+        <v>102229.41</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -6554,25 +6554,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="F74" t="n">
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>6957.43</v>
+        <v>7206.55</v>
       </c>
       <c r="H74" t="n">
-        <v>6965.7</v>
+        <v>7223.26</v>
       </c>
       <c r="J74" t="n">
-        <v>6920.93</v>
+        <v>7171</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -6580,16 +6580,16 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>4.4135</v>
+        <v>2.1275</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>4.4135</v>
+        <v>2.1275</v>
       </c>
       <c r="N74" t="n">
         <v>100000</v>
       </c>
       <c r="O74" t="n">
-        <v>104413.54</v>
+        <v>102127.47</v>
       </c>
     </row>
     <row r="75">
@@ -6599,7 +6599,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -6608,25 +6608,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="F75" t="n">
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>6982.4</v>
+        <v>6957.43</v>
       </c>
       <c r="H75" t="n">
-        <v>6988.83</v>
+        <v>6965.7</v>
       </c>
       <c r="J75" t="n">
-        <v>6978.6</v>
+        <v>6920.93</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -6634,16 +6634,16 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0.591</v>
+        <v>4.4135</v>
       </c>
       <c r="M75" s="2" t="n">
-        <v>0.591</v>
+        <v>4.4135</v>
       </c>
       <c r="N75" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O75" t="n">
         <v>104413.54</v>
-      </c>
-      <c r="O75" t="n">
-        <v>105030.61</v>
       </c>
     </row>
     <row r="76">
@@ -6653,7 +6653,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -6662,12 +6662,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -6677,10 +6677,10 @@
         <v>6982.4</v>
       </c>
       <c r="H76" t="n">
-        <v>6992.85</v>
+        <v>6988.83</v>
       </c>
       <c r="J76" t="n">
-        <v>6969.01</v>
+        <v>6978.6</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -6688,16 +6688,16 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.2813</v>
+        <v>0.591</v>
       </c>
       <c r="M76" s="2" t="n">
-        <v>1.2813</v>
+        <v>0.591</v>
       </c>
       <c r="N76" t="n">
+        <v>104413.54</v>
+      </c>
+      <c r="O76" t="n">
         <v>105030.61</v>
-      </c>
-      <c r="O76" t="n">
-        <v>106376.4</v>
       </c>
     </row>
     <row r="77">
@@ -6707,7 +6707,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -6716,12 +6716,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -6731,10 +6731,10 @@
         <v>6982.4</v>
       </c>
       <c r="H77" t="n">
-        <v>6991.93</v>
+        <v>6992.85</v>
       </c>
       <c r="J77" t="n">
-        <v>6976.44</v>
+        <v>6969.01</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -6742,16 +6742,16 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0.6254</v>
+        <v>1.2813</v>
       </c>
       <c r="M77" s="2" t="n">
-        <v>0.6254</v>
+        <v>1.2813</v>
       </c>
       <c r="N77" t="n">
+        <v>105030.61</v>
+      </c>
+      <c r="O77" t="n">
         <v>106376.4</v>
-      </c>
-      <c r="O77" t="n">
-        <v>107041.68</v>
       </c>
     </row>
     <row r="78">
@@ -6761,7 +6761,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -6770,12 +6770,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -6785,10 +6785,10 @@
         <v>6982.4</v>
       </c>
       <c r="H78" t="n">
-        <v>6986.84</v>
+        <v>6991.93</v>
       </c>
       <c r="J78" t="n">
-        <v>6941.81</v>
+        <v>6976.44</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -6796,16 +6796,16 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>9.1419</v>
+        <v>0.6254</v>
       </c>
       <c r="M78" s="2" t="n">
-        <v>9.1419</v>
+        <v>0.6254</v>
       </c>
       <c r="N78" t="n">
+        <v>106376.4</v>
+      </c>
+      <c r="O78" t="n">
         <v>107041.68</v>
-      </c>
-      <c r="O78" t="n">
-        <v>116827.31</v>
       </c>
     </row>
     <row r="79">
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -6824,12 +6824,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -6839,10 +6839,10 @@
         <v>6982.4</v>
       </c>
       <c r="H79" t="n">
-        <v>6993.49</v>
+        <v>6986.84</v>
       </c>
       <c r="J79" t="n">
-        <v>6941.47</v>
+        <v>6941.81</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -6850,16 +6850,16 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>3.6907</v>
+        <v>9.1419</v>
       </c>
       <c r="M79" s="2" t="n">
-        <v>3.6907</v>
+        <v>9.1419</v>
       </c>
       <c r="N79" t="n">
+        <v>107041.68</v>
+      </c>
+      <c r="O79" t="n">
         <v>116827.31</v>
-      </c>
-      <c r="O79" t="n">
-        <v>121139.07</v>
       </c>
     </row>
     <row r="80">
@@ -6869,34 +6869,34 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="F80" t="n">
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>6794.4</v>
+        <v>6982.4</v>
       </c>
       <c r="H80" t="n">
-        <v>6770.77</v>
+        <v>6993.49</v>
       </c>
       <c r="J80" t="n">
-        <v>6830.71</v>
+        <v>6941.47</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -6904,53 +6904,53 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.5366</v>
+        <v>3.6907</v>
       </c>
       <c r="M80" s="2" t="n">
-        <v>1.5366</v>
+        <v>3.6907</v>
       </c>
       <c r="N80" t="n">
+        <v>116827.31</v>
+      </c>
+      <c r="O80" t="n">
         <v>121139.07</v>
-      </c>
-      <c r="O80" t="n">
-        <v>123000.5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F81" t="n">
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>86.081</v>
+        <v>6794.4</v>
       </c>
       <c r="H81" t="n">
-        <v>88.001</v>
+        <v>6770.77</v>
       </c>
       <c r="J81" t="n">
-        <v>85.59099999999999</v>
+        <v>6830.71</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -6958,16 +6958,16 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0.2552</v>
+        <v>1.5366</v>
       </c>
       <c r="M81" s="2" t="n">
-        <v>0.2552</v>
+        <v>1.5366</v>
       </c>
       <c r="N81" t="n">
-        <v>100000</v>
+        <v>121139.07</v>
       </c>
       <c r="O81" t="n">
-        <v>100255.21</v>
+        <v>123000.5</v>
       </c>
     </row>
     <row r="82">
@@ -6977,34 +6977,34 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="F82" t="n">
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>73.84399999999999</v>
+        <v>86.081</v>
       </c>
       <c r="H82" t="n">
-        <v>71.999</v>
+        <v>88.001</v>
       </c>
       <c r="J82" t="n">
-        <v>75.91200000000001</v>
+        <v>85.59099999999999</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -7012,53 +7012,53 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.1209</v>
+        <v>0.2552</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>1.1209</v>
+        <v>0.2552</v>
       </c>
       <c r="N82" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O82" t="n">
         <v>100255.21</v>
-      </c>
-      <c r="O82" t="n">
-        <v>101378.94</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sugar_World_CSCE_Futures</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F83" t="n">
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>15</v>
+        <v>73.84399999999999</v>
       </c>
       <c r="H83" t="n">
-        <v>15.26</v>
+        <v>71.999</v>
       </c>
       <c r="J83" t="n">
-        <v>14.99</v>
+        <v>75.91200000000001</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -7066,16 +7066,16 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0.0385</v>
+        <v>1.1209</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>0.0385</v>
+        <v>1.1209</v>
       </c>
       <c r="N83" t="n">
-        <v>100000</v>
+        <v>100255.21</v>
       </c>
       <c r="O83" t="n">
-        <v>100038.46</v>
+        <v>101378.94</v>
       </c>
     </row>
     <row r="84">
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -7094,12 +7094,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -7109,10 +7109,10 @@
         <v>15</v>
       </c>
       <c r="H84" t="n">
-        <v>15.18</v>
+        <v>15.26</v>
       </c>
       <c r="J84" t="n">
-        <v>14.85</v>
+        <v>14.99</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -7120,26 +7120,26 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0.8333</v>
+        <v>0.0385</v>
       </c>
       <c r="M84" s="2" t="n">
-        <v>0.8333</v>
+        <v>0.0385</v>
       </c>
       <c r="N84" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O84" t="n">
         <v>100038.46</v>
-      </c>
-      <c r="O84" t="n">
-        <v>100872.12</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund</t>
+          <t>Sugar_World_CSCE_Futures</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -7148,25 +7148,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F85" t="n">
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>20.89</v>
+        <v>15</v>
       </c>
       <c r="H85" t="n">
-        <v>21.07</v>
+        <v>15.18</v>
       </c>
       <c r="J85" t="n">
-        <v>20.88</v>
+        <v>14.85</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -7174,22 +7174,22 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0.0556</v>
+        <v>0.8333</v>
       </c>
       <c r="M85" s="2" t="n">
-        <v>0.0556</v>
+        <v>0.8333</v>
       </c>
       <c r="N85" t="n">
-        <v>100000</v>
+        <v>100038.46</v>
       </c>
       <c r="O85" t="n">
-        <v>100055.56</v>
+        <v>100872.12</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Teucrium_Wheat_Fund</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -7202,25 +7202,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="F86" t="n">
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>0.8614000000000001</v>
+        <v>20.89</v>
       </c>
       <c r="H86" t="n">
-        <v>0.8637</v>
+        <v>21.07</v>
       </c>
       <c r="J86" t="n">
-        <v>0.8589</v>
+        <v>20.88</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -7228,16 +7228,16 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.087</v>
+        <v>0.0556</v>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1.087</v>
+        <v>0.0556</v>
       </c>
       <c r="N86" t="n">
         <v>100000</v>
       </c>
       <c r="O86" t="n">
-        <v>101086.96</v>
+        <v>100055.56</v>
       </c>
     </row>
     <row r="87">
@@ -7247,7 +7247,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -7256,12 +7256,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -7271,10 +7271,10 @@
         <v>0.8614000000000001</v>
       </c>
       <c r="H87" t="n">
-        <v>0.8649</v>
+        <v>0.8637</v>
       </c>
       <c r="J87" t="n">
-        <v>0.8612</v>
+        <v>0.8589</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -7282,16 +7282,16 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0.0571</v>
+        <v>1.087</v>
       </c>
       <c r="M87" s="2" t="n">
-        <v>0.0571</v>
+        <v>1.087</v>
       </c>
       <c r="N87" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O87" t="n">
         <v>101086.96</v>
-      </c>
-      <c r="O87" t="n">
-        <v>101144.72</v>
       </c>
     </row>
     <row r="88">
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -7310,12 +7310,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F88" t="n">
@@ -7325,10 +7325,10 @@
         <v>0.8614000000000001</v>
       </c>
       <c r="H88" t="n">
-        <v>0.8658</v>
+        <v>0.8649</v>
       </c>
       <c r="J88" t="n">
-        <v>0.8605</v>
+        <v>0.8612</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -7336,16 +7336,16 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0.2045</v>
+        <v>0.0571</v>
       </c>
       <c r="M88" s="2" t="n">
-        <v>0.2045</v>
+        <v>0.0571</v>
       </c>
       <c r="N88" t="n">
+        <v>101086.96</v>
+      </c>
+      <c r="O88" t="n">
         <v>101144.72</v>
-      </c>
-      <c r="O88" t="n">
-        <v>101351.61</v>
       </c>
     </row>
     <row r="89">
@@ -7355,34 +7355,34 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F89" t="n">
         <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>0.8467</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H89" t="n">
-        <v>0.8436</v>
+        <v>0.8658</v>
       </c>
       <c r="J89" t="n">
-        <v>0.8498</v>
+        <v>0.8605</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -7390,70 +7390,70 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1</v>
+        <v>0.2045</v>
       </c>
       <c r="M89" s="2" t="n">
-        <v>1</v>
+        <v>0.2045</v>
       </c>
       <c r="N89" t="n">
+        <v>101144.72</v>
+      </c>
+      <c r="O89" t="n">
         <v>101351.61</v>
-      </c>
-      <c r="O89" t="n">
-        <v>102365.12</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B90" t="n">
+        <v>4</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.8467</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0.8436</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0.8498</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>exit_close</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
         <v>1</v>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="F90" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" t="n">
-        <v>116.5</v>
-      </c>
-      <c r="H90" t="n">
-        <v>116.79</v>
-      </c>
-      <c r="J90" t="n">
-        <v>116.15</v>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>exit_close</t>
-        </is>
-      </c>
-      <c r="L90" t="n">
-        <v>1.2069</v>
-      </c>
       <c r="M90" s="2" t="n">
-        <v>1.2069</v>
+        <v>1</v>
       </c>
       <c r="N90" t="n">
-        <v>100000</v>
+        <v>101351.61</v>
       </c>
       <c r="O90" t="n">
-        <v>101206.9</v>
+        <v>102365.12</v>
       </c>
     </row>
     <row r="91">
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -7472,25 +7472,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="F91" t="n">
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>118.02</v>
+        <v>116.5</v>
       </c>
       <c r="H91" t="n">
-        <v>118.16</v>
+        <v>116.79</v>
       </c>
       <c r="J91" t="n">
-        <v>117.9</v>
+        <v>116.15</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -7498,16 +7498,16 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0.8571</v>
+        <v>1.2069</v>
       </c>
       <c r="M91" s="2" t="n">
-        <v>0.8571</v>
+        <v>1.2069</v>
       </c>
       <c r="N91" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O91" t="n">
         <v>101206.9</v>
-      </c>
-      <c r="O91" t="n">
-        <v>102074.38</v>
       </c>
     </row>
     <row r="92">
@@ -7517,7 +7517,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -7526,25 +7526,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="F92" t="n">
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>118.08</v>
+        <v>118.02</v>
       </c>
       <c r="H92" t="n">
         <v>118.16</v>
       </c>
       <c r="J92" t="n">
-        <v>117.84</v>
+        <v>117.9</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -7552,53 +7552,53 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>3</v>
+        <v>0.8571</v>
       </c>
       <c r="M92" s="2" t="n">
-        <v>3</v>
+        <v>0.8571</v>
       </c>
       <c r="N92" t="n">
+        <v>101206.9</v>
+      </c>
+      <c r="O92" t="n">
         <v>102074.38</v>
-      </c>
-      <c r="O92" t="n">
-        <v>105136.62</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="F93" t="n">
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>97.81399999999999</v>
+        <v>118.08</v>
       </c>
       <c r="H93" t="n">
-        <v>97.569</v>
+        <v>118.16</v>
       </c>
       <c r="J93" t="n">
-        <v>98.005</v>
+        <v>117.84</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -7606,16 +7606,16 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0.7796</v>
+        <v>3</v>
       </c>
       <c r="M93" s="2" t="n">
-        <v>0.7796</v>
+        <v>3</v>
       </c>
       <c r="N93" t="n">
-        <v>100000</v>
+        <v>102074.38</v>
       </c>
       <c r="O93" t="n">
-        <v>100779.59</v>
+        <v>105136.62</v>
       </c>
     </row>
     <row r="94">
@@ -7625,7 +7625,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -7634,25 +7634,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F94" t="n">
         <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>97.714</v>
+        <v>97.81399999999999</v>
       </c>
       <c r="H94" t="n">
-        <v>97.46899999999999</v>
+        <v>97.569</v>
       </c>
       <c r="J94" t="n">
-        <v>97.875</v>
+        <v>98.005</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -7660,16 +7660,16 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0.6571</v>
+        <v>0.7796</v>
       </c>
       <c r="M94" s="2" t="n">
-        <v>0.6571</v>
+        <v>0.7796</v>
       </c>
       <c r="N94" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O94" t="n">
         <v>100779.59</v>
-      </c>
-      <c r="O94" t="n">
-        <v>101441.86</v>
       </c>
     </row>
     <row r="95">
@@ -7679,34 +7679,34 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F95" t="n">
         <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>99.376</v>
+        <v>97.714</v>
       </c>
       <c r="H95" t="n">
-        <v>99.571</v>
+        <v>97.46899999999999</v>
       </c>
       <c r="J95" t="n">
-        <v>99.014</v>
+        <v>97.875</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -7714,16 +7714,16 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.8564</v>
+        <v>0.6571</v>
       </c>
       <c r="M95" s="2" t="n">
-        <v>1.8564</v>
+        <v>0.6571</v>
       </c>
       <c r="N95" t="n">
+        <v>100779.59</v>
+      </c>
+      <c r="O95" t="n">
         <v>101441.86</v>
-      </c>
-      <c r="O95" t="n">
-        <v>103325.03</v>
       </c>
     </row>
     <row r="96">
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -7742,12 +7742,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -7757,10 +7757,10 @@
         <v>99.376</v>
       </c>
       <c r="H96" t="n">
-        <v>99.46599999999999</v>
+        <v>99.571</v>
       </c>
       <c r="J96" t="n">
-        <v>99.218</v>
+        <v>99.014</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -7768,16 +7768,16 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.7556</v>
+        <v>1.8564</v>
       </c>
       <c r="M96" s="2" t="n">
-        <v>1.7556</v>
+        <v>1.8564</v>
       </c>
       <c r="N96" t="n">
+        <v>101441.86</v>
+      </c>
+      <c r="O96" t="n">
         <v>103325.03</v>
-      </c>
-      <c r="O96" t="n">
-        <v>105138.96</v>
       </c>
     </row>
     <row r="97">
@@ -7787,7 +7787,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -7796,25 +7796,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="F97" t="n">
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>99.246</v>
+        <v>99.376</v>
       </c>
       <c r="H97" t="n">
-        <v>99.501</v>
+        <v>99.46599999999999</v>
       </c>
       <c r="J97" t="n">
-        <v>98.96899999999999</v>
+        <v>99.218</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -7822,16 +7822,16 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.0863</v>
+        <v>1.7556</v>
       </c>
       <c r="M97" s="2" t="n">
-        <v>1.0863</v>
+        <v>1.7556</v>
       </c>
       <c r="N97" t="n">
+        <v>103325.03</v>
+      </c>
+      <c r="O97" t="n">
         <v>105138.96</v>
-      </c>
-      <c r="O97" t="n">
-        <v>106281.06</v>
       </c>
     </row>
     <row r="98">
@@ -7841,7 +7841,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -7850,25 +7850,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F98" t="n">
         <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>100.066</v>
+        <v>99.246</v>
       </c>
       <c r="H98" t="n">
-        <v>100.201</v>
+        <v>99.501</v>
       </c>
       <c r="J98" t="n">
-        <v>100.024</v>
+        <v>98.96899999999999</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -7876,16 +7876,16 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0.3111</v>
+        <v>1.0863</v>
       </c>
       <c r="M98" s="2" t="n">
-        <v>0.3111</v>
+        <v>1.0863</v>
       </c>
       <c r="N98" t="n">
+        <v>105138.96</v>
+      </c>
+      <c r="O98" t="n">
         <v>106281.06</v>
-      </c>
-      <c r="O98" t="n">
-        <v>106611.71</v>
       </c>
     </row>
     <row r="99">
@@ -7895,7 +7895,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -7904,12 +7904,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -7919,10 +7919,10 @@
         <v>100.066</v>
       </c>
       <c r="H99" t="n">
-        <v>100.316</v>
+        <v>100.201</v>
       </c>
       <c r="J99" t="n">
-        <v>99.849</v>
+        <v>100.024</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -7930,16 +7930,16 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0.868</v>
+        <v>0.3111</v>
       </c>
       <c r="M99" s="2" t="n">
-        <v>0.868</v>
+        <v>0.3111</v>
       </c>
       <c r="N99" t="n">
+        <v>106281.06</v>
+      </c>
+      <c r="O99" t="n">
         <v>106611.71</v>
-      </c>
-      <c r="O99" t="n">
-        <v>107537.1</v>
       </c>
     </row>
     <row r="100">
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -7958,12 +7958,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -7973,10 +7973,10 @@
         <v>100.066</v>
       </c>
       <c r="H100" t="n">
-        <v>100.361</v>
+        <v>100.316</v>
       </c>
       <c r="J100" t="n">
-        <v>99.866</v>
+        <v>99.849</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -7984,16 +7984,16 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0.678</v>
+        <v>0.868</v>
       </c>
       <c r="M100" s="2" t="n">
-        <v>0.678</v>
+        <v>0.868</v>
       </c>
       <c r="N100" t="n">
+        <v>106611.71</v>
+      </c>
+      <c r="O100" t="n">
         <v>107537.1</v>
-      </c>
-      <c r="O100" t="n">
-        <v>108266.17</v>
       </c>
     </row>
     <row r="101">
@@ -8003,7 +8003,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -8012,25 +8012,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F101" t="n">
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>100.621</v>
+        <v>100.066</v>
       </c>
       <c r="H101" t="n">
-        <v>100.911</v>
+        <v>100.361</v>
       </c>
       <c r="J101" t="n">
-        <v>100.618</v>
+        <v>99.866</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
@@ -8038,16 +8038,16 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0.0103</v>
+        <v>0.678</v>
       </c>
       <c r="M101" s="2" t="n">
-        <v>0.0103</v>
+        <v>0.678</v>
       </c>
       <c r="N101" t="n">
+        <v>107537.1</v>
+      </c>
+      <c r="O101" t="n">
         <v>108266.17</v>
-      </c>
-      <c r="O101" t="n">
-        <v>108277.37</v>
       </c>
     </row>
     <row r="102">
@@ -8057,7 +8057,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -8066,25 +8066,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F102" t="n">
         <v>0</v>
       </c>
       <c r="G102" t="n">
-        <v>101.411</v>
+        <v>100.621</v>
       </c>
       <c r="H102" t="n">
-        <v>101.526</v>
+        <v>100.911</v>
       </c>
       <c r="J102" t="n">
-        <v>101.193</v>
+        <v>100.618</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -8092,26 +8092,26 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.8957</v>
+        <v>0.0103</v>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1.8957</v>
+        <v>0.0103</v>
       </c>
       <c r="N102" t="n">
+        <v>108266.17</v>
+      </c>
+      <c r="O102" t="n">
         <v>108277.37</v>
-      </c>
-      <c r="O102" t="n">
-        <v>110329.93</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -8120,25 +8120,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F103" t="n">
         <v>0</v>
       </c>
       <c r="G103" t="n">
-        <v>121.72</v>
+        <v>101.411</v>
       </c>
       <c r="H103" t="n">
-        <v>123.03</v>
+        <v>101.526</v>
       </c>
       <c r="J103" t="n">
-        <v>121.43</v>
+        <v>101.193</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -8146,69 +8146,177 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0.2214</v>
+        <v>1.8957</v>
       </c>
       <c r="M103" s="2" t="n">
-        <v>0.2214</v>
+        <v>1.8957</v>
       </c>
       <c r="N103" t="n">
-        <v>100000</v>
+        <v>108277.37</v>
       </c>
       <c r="O103" t="n">
-        <v>100221.37</v>
+        <v>110329.93</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>11</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" t="n">
+        <v>101.411</v>
+      </c>
+      <c r="H104" t="n">
+        <v>101.491</v>
+      </c>
+      <c r="J104" t="n">
+        <v>101.266</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>exit_close</t>
+        </is>
+      </c>
+      <c r="L104" t="n">
+        <v>1.8125</v>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>1.8125</v>
+      </c>
+      <c r="N104" t="n">
+        <v>110329.93</v>
+      </c>
+      <c r="O104" t="n">
+        <v>112329.66</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
           <t>United_States_Oil_Fund_LP</t>
         </is>
       </c>
-      <c r="B104" t="n">
+      <c r="B105" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" t="n">
+        <v>121.72</v>
+      </c>
+      <c r="H105" t="n">
+        <v>123.03</v>
+      </c>
+      <c r="J105" t="n">
+        <v>121.43</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>exit_close</t>
+        </is>
+      </c>
+      <c r="L105" t="n">
+        <v>0.2214</v>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>0.2214</v>
+      </c>
+      <c r="N105" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O105" t="n">
+        <v>100221.37</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>United_States_Oil_Fund_LP</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
         <v>2</v>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>short</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="E106" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="F104" t="n">
-        <v>0</v>
-      </c>
-      <c r="G104" t="n">
+      <c r="F106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" t="n">
         <v>130.16</v>
       </c>
-      <c r="H104" t="n">
+      <c r="H106" t="n">
         <v>130.94</v>
       </c>
-      <c r="J104" t="n">
+      <c r="J106" t="n">
         <v>127.25</v>
       </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>exit_close</t>
-        </is>
-      </c>
-      <c r="L104" t="n">
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>exit_close</t>
+        </is>
+      </c>
+      <c r="L106" t="n">
         <v>3.7308</v>
       </c>
-      <c r="M104" s="2" t="n">
+      <c r="M106" s="2" t="n">
         <v>3.7308</v>
       </c>
-      <c r="N104" t="n">
+      <c r="N106" t="n">
         <v>100221.37</v>
       </c>
-      <c r="O104" t="n">
+      <c r="O106" t="n">
         <v>103960.4</v>
       </c>
     </row>

--- a/output/quickfixclose_all_markets_daily.xlsx
+++ b/output/quickfixclose_all_markets_daily.xlsx
@@ -549,11 +549,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F2" t="n">
         <v>7</v>
@@ -597,11 +597,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F3" t="n">
         <v>6</v>
@@ -645,11 +645,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F4" t="n">
         <v>10</v>
@@ -693,11 +693,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F5" t="n">
         <v>11</v>
@@ -741,11 +741,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
@@ -789,11 +789,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F7" t="n">
         <v>3</v>
@@ -837,11 +837,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -885,11 +885,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F9" t="n">
         <v>3</v>
@@ -933,11 +933,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
@@ -981,11 +981,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F11" t="n">
         <v>4</v>
@@ -1029,11 +1029,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F12" t="n">
         <v>4</v>
@@ -1077,11 +1077,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F13" t="n">
         <v>3</v>
@@ -1125,11 +1125,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
@@ -1173,11 +1173,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
@@ -1221,11 +1221,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F16" t="n">
         <v>3</v>
@@ -1269,11 +1269,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F17" t="n">
         <v>2</v>
@@ -1317,11 +1317,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F18" t="n">
         <v>2</v>
@@ -1365,11 +1365,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F19" t="n">
         <v>2</v>
@@ -1413,11 +1413,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
@@ -1461,11 +1461,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1506,11 +1506,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1551,11 +1551,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1596,11 +1596,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1641,11 +1641,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1686,11 +1686,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -2538,7 +2538,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixclose daily (exit = the entry bar's own close, flat the same day), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-29); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-30 20:33 UTC.</t>
+          <t>quickfixclose daily (exit = the entry bar's own close, flat the same day), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-30); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-31 15:45 UTC.</t>
         </is>
       </c>
     </row>
